--- a/01_normalization/c_data/05_normalization_supp.xlsx
+++ b/01_normalization/c_data/05_normalization_supp.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Per-Sample Outlier Diagnostics</t>
   </si>
   <si>
-    <t xml:space="preserve">miss_flag/pca_flag/mad_flag: per-method | consensus_outlier: TRUE if all 3 agree</t>
+    <t xml:space="preserve">miss_flag/pca_flag/mad_flag/cor_flag: per-method | consensus_outlier: TRUE if ≥3 of 4 agree</t>
   </si>
   <si>
     <t xml:space="preserve">Col_ID</t>
@@ -7234,7 +7234,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="69.31" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="80.4575" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="5.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="9.71" hidden="0" customWidth="1"/>
@@ -7342,19 +7342,19 @@
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>3.12737458791793</v>
+        <v>3.1273747320112</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>21.2552159089682</v>
+        <v>21.2552153325773</v>
       </c>
       <c r="L5" t="b">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.96912429433871</v>
+        <v>0.969124267733397</v>
       </c>
       <c r="N5" t="b">
         <v>0</v>
@@ -7395,19 +7395,19 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0.922429526189328</v>
+        <v>0.92242955024705</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>20.6443853039901</v>
+        <v>20.6443844237615</v>
       </c>
       <c r="L6" t="b">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.97678249651008</v>
+        <v>0.97678241355347</v>
       </c>
       <c r="N6" t="b">
         <v>0</v>
@@ -7448,19 +7448,19 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>2.71785706159602</v>
+        <v>2.71785739946698</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>20.4931205301316</v>
+        <v>20.4931195526002</v>
       </c>
       <c r="L7" t="b">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.977879691870538</v>
+        <v>0.977879655114263</v>
       </c>
       <c r="N7" t="b">
         <v>0</v>
@@ -7501,19 +7501,19 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>5.51952576001667</v>
+        <v>5.5195254919038</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>20.9591196966588</v>
+        <v>20.9591189889559</v>
       </c>
       <c r="L8" t="b">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.975758124008541</v>
+        <v>0.97575809074707</v>
       </c>
       <c r="N8" t="b">
         <v>0</v>
@@ -7554,19 +7554,19 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0.159978898796426</v>
+        <v>0.159978895745367</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>20.9258365889341</v>
+        <v>20.9258358647088</v>
       </c>
       <c r="L9" t="b">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.968879648434617</v>
+        <v>0.968879607223337</v>
       </c>
       <c r="N9" t="b">
         <v>0</v>
@@ -7607,19 +7607,19 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>5.69189555538045</v>
+        <v>5.69189544844408</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>20.7933897784219</v>
+        <v>20.7933889845679</v>
       </c>
       <c r="L10" t="b">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.974694407821234</v>
+        <v>0.974694359623878</v>
       </c>
       <c r="N10" t="b">
         <v>0</v>
@@ -7660,19 +7660,19 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>5.11490829317144</v>
+        <v>5.11490895355509</v>
       </c>
       <c r="J11" t="b">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>20.7700371390405</v>
+        <v>20.770036332232</v>
       </c>
       <c r="L11" t="b">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0.974028855705947</v>
+        <v>0.974053024851074</v>
       </c>
       <c r="N11" t="b">
         <v>0</v>
@@ -7713,19 +7713,19 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>2.46842610664661</v>
+        <v>2.46842608488957</v>
       </c>
       <c r="J12" t="b">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>21.1146936104443</v>
+        <v>21.1146929750863</v>
       </c>
       <c r="L12" t="b">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.977900092866108</v>
+        <v>0.977900061472529</v>
       </c>
       <c r="N12" t="b">
         <v>0</v>
@@ -7766,19 +7766,19 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0.699319454872561</v>
+        <v>0.699319454435606</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>20.7590469832376</v>
+        <v>20.7590461702595</v>
       </c>
       <c r="L13" t="b">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0.97736044152188</v>
+        <v>0.9770515692259</v>
       </c>
       <c r="N13" t="b">
         <v>0</v>
@@ -7819,19 +7819,19 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0.412490155105468</v>
+        <v>0.412490126262406</v>
       </c>
       <c r="J14" t="b">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>20.6990208252302</v>
+        <v>20.699019977713</v>
       </c>
       <c r="L14" t="b">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.980403632482922</v>
+        <v>0.980403583572173</v>
       </c>
       <c r="N14" t="b">
         <v>0</v>
@@ -7872,19 +7872,19 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>6.79493467980961</v>
+        <v>6.79493660417385</v>
       </c>
       <c r="J15" t="b">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>20.4411134206974</v>
+        <v>20.4411124072845</v>
       </c>
       <c r="L15" t="b">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.965440185784528</v>
+        <v>0.965440165158427</v>
       </c>
       <c r="N15" t="b">
         <v>0</v>
@@ -7925,19 +7925,19 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>2.92367284530103</v>
+        <v>2.92367271981756</v>
       </c>
       <c r="J16" t="b">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>20.9144296608954</v>
+        <v>20.9144289309271</v>
       </c>
       <c r="L16" t="b">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.978711712945274</v>
+        <v>0.978711664132153</v>
       </c>
       <c r="N16" t="b">
         <v>0</v>
@@ -7978,19 +7978,19 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>1.93865307218879</v>
+        <v>1.93865308286289</v>
       </c>
       <c r="J17" t="b">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>20.724891004462</v>
+        <v>20.7248901720069</v>
       </c>
       <c r="L17" t="b">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.979132352391718</v>
+        <v>0.978732218514252</v>
       </c>
       <c r="N17" t="b">
         <v>0</v>
@@ -8031,19 +8031,19 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>2.06752819026894</v>
+        <v>2.06752824315255</v>
       </c>
       <c r="J18" t="b">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>20.6308545580467</v>
+        <v>20.6308536695238</v>
       </c>
       <c r="L18" t="b">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.975268938176</v>
+        <v>0.975268906799824</v>
       </c>
       <c r="N18" t="b">
         <v>0</v>
@@ -8084,19 +8084,19 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>4.53299117953077</v>
+        <v>4.53299106563924</v>
       </c>
       <c r="J19" t="b">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>20.8065157958381</v>
+        <v>20.806515009174</v>
       </c>
       <c r="L19" t="b">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.975874668356751</v>
+        <v>0.975874634663539</v>
       </c>
       <c r="N19" t="b">
         <v>0</v>
@@ -8137,19 +8137,19 @@
         <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>2.66653279416088</v>
+        <v>2.66653302633753</v>
       </c>
       <c r="J20" t="b">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>20.6084976436614</v>
+        <v>20.6084967412605</v>
       </c>
       <c r="L20" t="b">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.977783565321787</v>
+        <v>0.977668174164438</v>
       </c>
       <c r="N20" t="b">
         <v>0</v>
@@ -8190,19 +8190,19 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>3.22294951921304</v>
+        <v>3.22294953070057</v>
       </c>
       <c r="J21" t="b">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>20.8887558812226</v>
+        <v>20.8887551381478</v>
       </c>
       <c r="L21" t="b">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.974159812708332</v>
+        <v>0.974642158027066</v>
       </c>
       <c r="N21" t="b">
         <v>0</v>
@@ -8243,19 +8243,19 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>0.874250004169871</v>
+        <v>0.87424999380481</v>
       </c>
       <c r="J22" t="b">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>20.7357551541754</v>
+        <v>20.7357543279655</v>
       </c>
       <c r="L22" t="b">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.980291845016369</v>
+        <v>0.980291807482942</v>
       </c>
       <c r="N22" t="b">
         <v>0</v>
@@ -8296,19 +8296,19 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>3.69142940702731</v>
+        <v>3.69142937273159</v>
       </c>
       <c r="J23" t="b">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>21.0765161083547</v>
+        <v>21.076515455959</v>
       </c>
       <c r="L23" t="b">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.974364515612546</v>
+        <v>0.974364476865657</v>
       </c>
       <c r="N23" t="b">
         <v>0</v>
@@ -8349,19 +8349,19 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>1.29231285297377</v>
+        <v>1.29231288290357</v>
       </c>
       <c r="J24" t="b">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>20.6625006210381</v>
+        <v>20.6624997517931</v>
       </c>
       <c r="L24" t="b">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.978240239154472</v>
+        <v>0.978336761757953</v>
       </c>
       <c r="N24" t="b">
         <v>0</v>
@@ -8402,19 +8402,19 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>4.89991747476295</v>
+        <v>4.89991739086359</v>
       </c>
       <c r="J25" t="b">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>20.8612845903916</v>
+        <v>20.8612838330318</v>
       </c>
       <c r="L25" t="b">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.974072007668672</v>
+        <v>0.97401208055495</v>
       </c>
       <c r="N25" t="b">
         <v>0</v>
@@ -8455,19 +8455,19 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>0.677741313259834</v>
+        <v>0.677741300048152</v>
       </c>
       <c r="J26" t="b">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>20.7823287947688</v>
+        <v>20.7823279948051</v>
       </c>
       <c r="L26" t="b">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.982299907753</v>
+        <v>0.982299862904105</v>
       </c>
       <c r="N26" t="b">
         <v>0</v>
@@ -8508,19 +8508,19 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0.371436639560419</v>
+        <v>0.371436652814456</v>
       </c>
       <c r="J27" t="b">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>20.8540187291858</v>
+        <v>20.8540179679942</v>
       </c>
       <c r="L27" t="b">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.98051629922935</v>
+        <v>0.980704597051324</v>
       </c>
       <c r="N27" t="b">
         <v>0</v>
@@ -8561,19 +8561,19 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>1.37941196938643</v>
+        <v>1.37941201412198</v>
       </c>
       <c r="J28" t="b">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>20.8082847045578</v>
+        <v>20.8082839188577</v>
       </c>
       <c r="L28" t="b">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.974772008832201</v>
+        <v>0.974771923600739</v>
       </c>
       <c r="N28" t="b">
         <v>0</v>
@@ -8614,19 +8614,19 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>1.87144994176074</v>
+        <v>1.87144993596244</v>
       </c>
       <c r="J29" t="b">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>20.6948832449587</v>
+        <v>20.6948823950074</v>
       </c>
       <c r="L29" t="b">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.978505200351964</v>
+        <v>0.978576660058435</v>
       </c>
       <c r="N29" t="b">
         <v>0</v>
@@ -8667,19 +8667,19 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>1.42777867894737</v>
+        <v>1.42777870106479</v>
       </c>
       <c r="J30" t="b">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>20.5948000029106</v>
+        <v>20.5947990919026</v>
       </c>
       <c r="L30" t="b">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.979076275878501</v>
+        <v>0.979223387469464</v>
       </c>
       <c r="N30" t="b">
         <v>0</v>
@@ -8720,19 +8720,19 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>0.966231589141581</v>
+        <v>0.966231504792723</v>
       </c>
       <c r="J31" t="b">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>20.8251412467575</v>
+        <v>20.8251404701842</v>
       </c>
       <c r="L31" t="b">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.97781630724831</v>
+        <v>0.977816263608948</v>
       </c>
       <c r="N31" t="b">
         <v>0</v>
@@ -8773,19 +8773,19 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>2.54964902413116</v>
+        <v>2.54964926564619</v>
       </c>
       <c r="J32" t="b">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>20.7178228255714</v>
+        <v>20.7178219890279</v>
       </c>
       <c r="L32" t="b">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.969794536508579</v>
+        <v>0.969794477609723</v>
       </c>
       <c r="N32" t="b">
         <v>0</v>
@@ -8826,19 +8826,19 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0.254363850865908</v>
+        <v>0.254363825394767</v>
       </c>
       <c r="J33" t="b">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>20.6687716115527</v>
+        <v>20.6687707460778</v>
       </c>
       <c r="L33" t="b">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.981076169624759</v>
+        <v>0.981076122533435</v>
       </c>
       <c r="N33" t="b">
         <v>0</v>
@@ -8879,19 +8879,19 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>2.76043307695514</v>
+        <v>2.76043313986045</v>
       </c>
       <c r="J34" t="b">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>20.5905806541984</v>
+        <v>20.5905797405223</v>
       </c>
       <c r="L34" t="b">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.977937313936995</v>
+        <v>0.977937289681314</v>
       </c>
       <c r="N34" t="b">
         <v>0</v>
@@ -8932,19 +8932,19 @@
         <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>2.29018627200592</v>
+        <v>2.29018616728373</v>
       </c>
       <c r="J35" t="b">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>21.3554914342734</v>
+        <v>21.3554908965844</v>
       </c>
       <c r="L35" t="b">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.9766171835221</v>
+        <v>0.976617138149132</v>
       </c>
       <c r="N35" t="b">
         <v>0</v>
@@ -8985,19 +8985,19 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>7.29297017140843</v>
+        <v>7.29297009825523</v>
       </c>
       <c r="J36" t="b">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>21.6201522441396</v>
+        <v>21.6201517965703</v>
       </c>
       <c r="L36" t="b">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.961611158481067</v>
+        <v>0.96161114149645</v>
       </c>
       <c r="N36" t="b">
         <v>1</v>
@@ -9038,19 +9038,19 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>0.685283661950229</v>
+        <v>0.685283687684554</v>
       </c>
       <c r="J37" t="b">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>20.6744027630632</v>
+        <v>20.6744019009595</v>
       </c>
       <c r="L37" t="b">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.981390501976386</v>
+        <v>0.981390460531674</v>
       </c>
       <c r="N37" t="b">
         <v>0</v>
@@ -9091,19 +9091,19 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>2.00797086088412</v>
+        <v>2.00797079533516</v>
       </c>
       <c r="J38" t="b">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>21.5221111875445</v>
+        <v>21.5221107085025</v>
       </c>
       <c r="L38" t="b">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.974526789942667</v>
+        <v>0.97476173261885</v>
       </c>
       <c r="N38" t="b">
         <v>0</v>
@@ -9144,19 +9144,19 @@
         <v>1</v>
       </c>
       <c r="I39" t="n">
-        <v>14.182101518722</v>
+        <v>14.182100270707</v>
       </c>
       <c r="J39" t="b">
         <v>1</v>
       </c>
       <c r="K39" t="n">
-        <v>22.8873645085676</v>
+        <v>22.8873643226196</v>
       </c>
       <c r="L39" t="b">
         <v>1</v>
       </c>
       <c r="M39" t="n">
-        <v>0.900936081566821</v>
+        <v>0.901913105205344</v>
       </c>
       <c r="N39" t="b">
         <v>1</v>
@@ -9197,19 +9197,19 @@
         <v>1</v>
       </c>
       <c r="I40" t="n">
-        <v>2.04829621176392</v>
+        <v>2.04829622256877</v>
       </c>
       <c r="J40" t="b">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>22.0042715665328</v>
+        <v>22.0042712235844</v>
       </c>
       <c r="L40" t="b">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.967216284122984</v>
+        <v>0.967216264336164</v>
       </c>
       <c r="N40" t="b">
         <v>0</v>
@@ -9250,19 +9250,19 @@
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>2.39351009493631</v>
+        <v>2.39351025542787</v>
       </c>
       <c r="J41" t="b">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>21.6822483860718</v>
+        <v>21.682247957358</v>
       </c>
       <c r="L41" t="b">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.967791336479466</v>
+        <v>0.967785075140808</v>
       </c>
       <c r="N41" t="b">
         <v>0</v>
@@ -9303,19 +9303,19 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>5.04429762333763</v>
+        <v>5.04429756400002</v>
       </c>
       <c r="J42" t="b">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>21.8657543821506</v>
+        <v>21.8657540046419</v>
       </c>
       <c r="L42" t="b">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.966370117756335</v>
+        <v>0.966370078565969</v>
       </c>
       <c r="N42" t="b">
         <v>0</v>
@@ -9356,19 +9356,19 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>0.626201618586195</v>
+        <v>0.626201588949882</v>
       </c>
       <c r="J43" t="b">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>21.019775292027</v>
+        <v>21.0197746134615</v>
       </c>
       <c r="L43" t="b">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.980601555294004</v>
+        <v>0.980601511861024</v>
       </c>
       <c r="N43" t="b">
         <v>0</v>
@@ -9409,19 +9409,19 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>0.405821575113482</v>
+        <v>0.405821630142739</v>
       </c>
       <c r="J44" t="b">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>21.1169537132122</v>
+        <v>21.1169530788487</v>
       </c>
       <c r="L44" t="b">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.978579231258905</v>
+        <v>0.978579179866961</v>
       </c>
       <c r="N44" t="b">
         <v>0</v>
@@ -9462,19 +9462,19 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>2.31986261566148</v>
+        <v>2.3198626318318</v>
       </c>
       <c r="J45" t="b">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>21.0038823640786</v>
+        <v>21.0038816779892</v>
       </c>
       <c r="L45" t="b">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.977049744927881</v>
+        <v>0.977067816668197</v>
       </c>
       <c r="N45" t="b">
         <v>0</v>
@@ -9515,19 +9515,19 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>0.6094414087021</v>
+        <v>0.609441409268822</v>
       </c>
       <c r="J46" t="b">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>21.3144300126271</v>
+        <v>21.3144294594148</v>
       </c>
       <c r="L46" t="b">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.977893259299423</v>
+        <v>0.977893240923999</v>
       </c>
       <c r="N46" t="b">
         <v>0</v>
@@ -9568,19 +9568,19 @@
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>0.375817534561769</v>
+        <v>0.375817515109966</v>
       </c>
       <c r="J47" t="b">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>21.0904613986867</v>
+        <v>21.0904607525665</v>
       </c>
       <c r="L47" t="b">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.981577121209405</v>
+        <v>0.981577087389189</v>
       </c>
       <c r="N47" t="b">
         <v>0</v>
@@ -9621,19 +9621,19 @@
         <v>1</v>
       </c>
       <c r="I48" t="n">
-        <v>0.378006859907463</v>
+        <v>0.378006926830685</v>
       </c>
       <c r="J48" t="b">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>21.8544936724408</v>
+        <v>21.8544932919742</v>
       </c>
       <c r="L48" t="b">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.973163200755801</v>
+        <v>0.973163179655773</v>
       </c>
       <c r="N48" t="b">
         <v>0</v>
@@ -9674,19 +9674,19 @@
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>1.25206311878269</v>
+        <v>1.25206302942827</v>
       </c>
       <c r="J49" t="b">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>21.1692643303135</v>
+        <v>21.1692637185381</v>
       </c>
       <c r="L49" t="b">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.979054544607796</v>
+        <v>0.979054517578125</v>
       </c>
       <c r="N49" t="b">
         <v>0</v>
@@ -9727,19 +9727,19 @@
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>2.63982372142276</v>
+        <v>2.63982374367008</v>
       </c>
       <c r="J50" t="b">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>21.2176459594219</v>
+        <v>21.2176453678238</v>
       </c>
       <c r="L50" t="b">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0.977103081762287</v>
+        <v>0.977103055132668</v>
       </c>
       <c r="N50" t="b">
         <v>0</v>
@@ -9780,19 +9780,19 @@
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>1.31133033269348</v>
+        <v>1.31133023631268</v>
       </c>
       <c r="J51" t="b">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>21.0053346577004</v>
+        <v>21.0053339723087</v>
       </c>
       <c r="L51" t="b">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0.976983690469748</v>
+        <v>0.977022093024328</v>
       </c>
       <c r="N51" t="b">
         <v>0</v>
@@ -9833,19 +9833,19 @@
         <v>1</v>
       </c>
       <c r="I52" t="n">
-        <v>3.10009786774254</v>
+        <v>3.10009799674634</v>
       </c>
       <c r="J52" t="b">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>20.5938436774459</v>
+        <v>20.5938427658284</v>
       </c>
       <c r="L52" t="b">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0.97192382384219</v>
+        <v>0.971395294686571</v>
       </c>
       <c r="N52" t="b">
         <v>0</v>
@@ -9886,19 +9886,19 @@
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>2.21046392216271</v>
+        <v>2.21046386364207</v>
       </c>
       <c r="J53" t="b">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>21.4672404475147</v>
+        <v>21.467239949901</v>
       </c>
       <c r="L53" t="b">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>0.971017921625374</v>
+        <v>0.971017895887401</v>
       </c>
       <c r="N53" t="b">
         <v>0</v>
@@ -9939,19 +9939,19 @@
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>10.7893574059066</v>
+        <v>10.7893579671628</v>
       </c>
       <c r="J54" t="b">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>20.4872077295582</v>
+        <v>20.4872067480114</v>
       </c>
       <c r="L54" t="b">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0.966229173865458</v>
+        <v>0.966229126210567</v>
       </c>
       <c r="N54" t="b">
         <v>0</v>
@@ -9992,19 +9992,19 @@
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>0.444328074769601</v>
+        <v>0.444328141383918</v>
       </c>
       <c r="J55" t="b">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>21.1177051869602</v>
+        <v>21.1177045529271</v>
       </c>
       <c r="L55" t="b">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0.980329320093026</v>
+        <v>0.980329286303885</v>
       </c>
       <c r="N55" t="b">
         <v>0</v>
@@ -10045,19 +10045,19 @@
         <v>1</v>
       </c>
       <c r="I56" t="n">
-        <v>4.66047741705177</v>
+        <v>4.66047713562924</v>
       </c>
       <c r="J56" t="b">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>21.9805646423179</v>
+        <v>21.9805642936864</v>
       </c>
       <c r="L56" t="b">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0.947825283233289</v>
+        <v>0.947825242708017</v>
       </c>
       <c r="N56" t="b">
         <v>1</v>
@@ -10098,19 +10098,19 @@
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>12.7269139622608</v>
+        <v>12.726912817077</v>
       </c>
       <c r="J57" t="b">
         <v>1</v>
       </c>
       <c r="K57" t="n">
-        <v>22.3240896038342</v>
+        <v>22.3240893290739</v>
       </c>
       <c r="L57" t="b">
         <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>0.957305374245313</v>
+        <v>0.957045536600974</v>
       </c>
       <c r="N57" t="b">
         <v>1</v>
@@ -10151,19 +10151,19 @@
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>8.00491401047993</v>
+        <v>8.00491298619975</v>
       </c>
       <c r="J58" t="b">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>21.7233205563888</v>
+        <v>21.723320139708</v>
       </c>
       <c r="L58" t="b">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>0.957383683325992</v>
+        <v>0.957383681772861</v>
       </c>
       <c r="N58" t="b">
         <v>1</v>
@@ -10204,19 +10204,19 @@
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>2.58770379279916</v>
+        <v>2.58770380211872</v>
       </c>
       <c r="J59" t="b">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>21.5614058910763</v>
+        <v>21.5614054249059</v>
       </c>
       <c r="L59" t="b">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>0.964408284134818</v>
+        <v>0.96440826098001</v>
       </c>
       <c r="N59" t="b">
         <v>1</v>
@@ -10257,19 +10257,19 @@
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>0.489220748477518</v>
+        <v>0.489220745105522</v>
       </c>
       <c r="J60" t="b">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>21.1951685209753</v>
+        <v>21.1951679200878</v>
       </c>
       <c r="L60" t="b">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>0.980328349098136</v>
+        <v>0.980328326104485</v>
       </c>
       <c r="N60" t="b">
         <v>0</v>
@@ -10310,19 +10310,19 @@
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>1.38232070271491</v>
+        <v>1.38232070222885</v>
       </c>
       <c r="J61" t="b">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>21.1016223656317</v>
+        <v>21.101621724491</v>
       </c>
       <c r="L61" t="b">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>0.980234887683053</v>
+        <v>0.980234846150034</v>
       </c>
       <c r="N61" t="b">
         <v>0</v>
@@ -10363,19 +10363,19 @@
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>3.89295365572461</v>
+        <v>3.8929537301101</v>
       </c>
       <c r="J62" t="b">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>20.6593368476004</v>
+        <v>20.6593359764467</v>
       </c>
       <c r="L62" t="b">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>0.974792237881385</v>
+        <v>0.974792186844665</v>
       </c>
       <c r="N62" t="b">
         <v>0</v>
@@ -10416,19 +10416,19 @@
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>4.84450500419646</v>
+        <v>4.84450496735979</v>
       </c>
       <c r="J63" t="b">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>21.2228839131612</v>
+        <v>21.2228833237072</v>
       </c>
       <c r="L63" t="b">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>0.971139595682564</v>
+        <v>0.97113954500742</v>
       </c>
       <c r="N63" t="b">
         <v>0</v>
@@ -10469,19 +10469,19 @@
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>3.0587202034179</v>
+        <v>3.0587202359383</v>
       </c>
       <c r="J64" t="b">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>20.8217436245279</v>
+        <v>20.8217428461235</v>
       </c>
       <c r="L64" t="b">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>0.976293425702289</v>
+        <v>0.976293398903052</v>
       </c>
       <c r="N64" t="b">
         <v>0</v>
@@ -10522,19 +10522,19 @@
         <v>1</v>
       </c>
       <c r="I65" t="n">
-        <v>1.54535898934936</v>
+        <v>1.54535903885501</v>
       </c>
       <c r="J65" t="b">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>21.4281693767945</v>
+        <v>21.4281688655214</v>
       </c>
       <c r="L65" t="b">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>0.973857369922537</v>
+        <v>0.973857331160763</v>
       </c>
       <c r="N65" t="b">
         <v>0</v>
@@ -10575,19 +10575,19 @@
         <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>2.05722593914766</v>
+        <v>2.05722603061726</v>
       </c>
       <c r="J66" t="b">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>20.8185244012568</v>
+        <v>20.8185236211131</v>
       </c>
       <c r="L66" t="b">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>0.977329862261978</v>
+        <v>0.977386657678976</v>
       </c>
       <c r="N66" t="b">
         <v>0</v>
@@ -10628,19 +10628,19 @@
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>1.0644062471848</v>
+        <v>1.06440622579931</v>
       </c>
       <c r="J67" t="b">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>21.1926391921071</v>
+        <v>21.1926385901651</v>
       </c>
       <c r="L67" t="b">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>0.978513962260055</v>
+        <v>0.97851391200384</v>
       </c>
       <c r="N67" t="b">
         <v>0</v>
@@ -10681,19 +10681,19 @@
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>6.2801733530652</v>
+        <v>6.28017345156404</v>
       </c>
       <c r="J68" t="b">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>20.8192037926329</v>
+        <v>20.819203012857</v>
       </c>
       <c r="L68" t="b">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>0.965328294400515</v>
+        <v>0.96532822989615</v>
       </c>
       <c r="N68" t="b">
         <v>0</v>
